--- a/test/33feats_importances.xlsx
+++ b/test/33feats_importances.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\iMTT\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59337A77-28B5-4D41-AC0F-BF14FDC69209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4924BCEF-53AD-409F-BE05-CF7D4C185484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="975" yWindow="4665" windowWidth="22095" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7020" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1_CN" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="76">
   <si>
     <t>[16] G density in loops</t>
   </si>
@@ -167,6 +168,990 @@
   </si>
   <si>
     <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[16] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[28] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[32] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两端环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[20] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[12] iM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[24] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[11] iM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[15] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[23] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[1] C-tract </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[31] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两端环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[19] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[27] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[4] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间环区的长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[8] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的环区的长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[6] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的两端的环区的长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[25] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[21] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[5] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的两端的环区的长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[7] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两端环区的长度之和</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[2] iM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[3] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环区长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[29] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[22] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最长的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[33] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两端环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[9] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的环区的长度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[18] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中间环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[26] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最短的两端的环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[17] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[30] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两端环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[14] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环区中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[13] iM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[10] iM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碱基的密度</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -178,7 +1163,7 @@
     <numFmt numFmtId="176" formatCode="0.0000"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +1183,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -309,13 +1301,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1275,99 +2267,99 @@
   <sheetData>
     <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14" t="s">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="14"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="17"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="11"/>
-      <c r="F5" s="17"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="15"/>
+      <c r="H5" s="14"/>
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="10"/>
-      <c r="D6" s="17"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="17"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="15"/>
+      <c r="H6" s="14"/>
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="15"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="10"/>
-      <c r="D7" s="17"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="11"/>
-      <c r="F7" s="17"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="15"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="10"/>
-      <c r="D8" s="17"/>
+      <c r="D8" s="16"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="17"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="14"/>
       <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="15"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="15"/>
+      <c r="D9" s="14"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="17"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="16"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="12"/>
-      <c r="D10" s="18"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="13"/>
-      <c r="F10" s="18"/>
+      <c r="F10" s="17"/>
       <c r="G10" s="12"/>
-      <c r="H10" s="16"/>
+      <c r="H10" s="15"/>
       <c r="I10" s="13"/>
     </row>
   </sheetData>
@@ -1381,4 +2373,674 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E767863-0089-424E-A625-79924F301143}">
+  <dimension ref="A2:F35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="33.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.42690555857184997</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0.48649485376056101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.418376080771035</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.45755248043802998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.40131157551253599</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.424593103877344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.358690663210191</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.41339308158064397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.33118055279271402</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.37193312559402902</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.29491671415335102</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0.36970216625583202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.259211616081792</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.35324949101251402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8.2697537870825497E-2</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.34633544175002201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.9733590556642502E-2</v>
+      </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.32270460983590399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.62294863953443E-2</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.31647211138648101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.5942798845802901E-2</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.19993186181516101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="6">
+        <v>9.1505554878445403E-3</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.15992659518664001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-6.3851379952201998E-2</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.148465569267756</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-6.5629714042347104E-2</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="8">
+        <v>6.7342668627231705E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-0.10571134203556699</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="8">
+        <v>4.8232381628700999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.14520582202271901</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="8">
+        <v>2.0964964433249699E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-0.14787349114121101</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1.23757381444032E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.15675969526064201</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="8">
+        <v>8.2330892980882198E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-0.16756300581627601</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3.5134233198324699E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.17947113963536401</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="8">
+        <v>-1.42701971306811E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.181563453736627</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="8">
+        <v>-2.8960092798163101E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-0.18528628804833</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="8">
+        <v>-0.28320669732798798</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.18748814464564101</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="8">
+        <v>-0.29436387868164599</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.202071670687443</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-0.32125218392260702</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-0.20547711269524899</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-0.33124577560889701</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-0.21174085896663</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="8">
+        <v>-0.34937695223211201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-0.22425081694111301</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="8">
+        <v>-0.368578345755533</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-0.225054412554716</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="8">
+        <v>-0.43068480580857799</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-0.24263740462952199</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="8">
+        <v>-0.454510523768268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-0.27313948755804202</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="8">
+        <v>-0.45987431600896</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-0.314138586256486</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-0.46231385716782403</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-0.318051345369329</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="8">
+        <v>-0.46724748239129399</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-0.37044616626221399</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-0.47277196683940798</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="9">
+        <f>VAR(C2:C34)</f>
+        <v>5.6127738916585929E-2</v>
+      </c>
+      <c r="F35" s="9">
+        <f>VAR(F2:F34)</f>
+        <v>0.1097790506391946</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B2:D34 F2:F34">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C34 F2:F34">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F34">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C34">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>